--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -4,71 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Test Cases" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Report" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Test Name</t>
-  </si>
-  <si>
-    <t>Objective</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Preconditions</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
-  </si>
-  <si>
-    <t>Test Data</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Execution Time</t>
-  </si>
-  <si>
-    <t>Failure Reason</t>
-  </si>
-  <si>
-    <t>Screenshot Path</t>
-  </si>
-  <si>
-    <t>Log Path</t>
-  </si>
-  <si>
-    <t>Source Test File</t>
-  </si>
-  <si>
-    <t>GitHub Run Number</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -76,22 +20,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="C00000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -106,9 +41,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -460,67 +394,16 @@
     <col min="7" max="7" width="50" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="55" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="35" customWidth="1"/>
-    <col min="14" max="16" width="30" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="35" customWidth="1"/>
+    <col min="17" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
